--- a/Employee_Reports_wi52/Roderick Cailao Amar Q0480.xlsx
+++ b/Employee_Reports_wi52/Roderick Cailao Amar Q0480.xlsx
@@ -581,11 +581,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -630,11 +630,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -679,11 +679,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -728,11 +728,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -777,11 +777,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -826,11 +826,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -875,11 +875,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -924,11 +924,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1037,53 +1037,53 @@
       <c r="K12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Truck dock (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-M-006</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>21-Aug-2024</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>21-Aug-2026</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1120,11 +1120,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1135,53 +1135,53 @@
       <c r="K14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Cool Room (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-M-011</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>29-Sep-2024</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>29-Sep-2026</t>
         </is>
       </c>
-      <c r="H15" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="H15" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1218,11 +1218,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1267,11 +1267,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1316,11 +1316,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1365,11 +1365,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-39</v>
+        <v>-47</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1537,11 +1537,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1586,11 +1586,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1635,11 +1635,11 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>-133</v>
+        <v>-141</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1684,11 +1684,11 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>-155</v>
+        <v>-163</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1782,11 +1782,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1831,11 +1831,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1880,11 +1880,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1929,11 +1929,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1966,11 +1966,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -1981,41 +1981,41 @@
       <c r="K32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr"/>
+      <c r="D33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>30-Sep-2025</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>30-Sep-2026</t>
         </is>
       </c>
-      <c r="H33" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
+      <c r="H33" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2052,11 +2052,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2089,11 +2089,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2126,11 +2126,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2163,11 +2163,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2200,11 +2200,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2237,11 +2237,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2274,11 +2274,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7991</v>
+        <v>7983</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7918</v>
+        <v>7910</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7921</v>
+        <v>7913</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7910</v>
+        <v>7902</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7917</v>
+        <v>7909</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7917</v>
+        <v>7909</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7910</v>
+        <v>7902</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7915</v>
+        <v>7907</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
